--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="49">
   <si>
     <t>Mat</t>
   </si>
@@ -100,6 +100,12 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -124,6 +130,12 @@
     <t>MORENO</t>
   </si>
   <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
     <t>KEVIN ISAAC</t>
   </si>
   <si>
@@ -146,6 +158,12 @@
   </si>
   <si>
     <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
   </si>
 </sst>
 </file>
@@ -920,7 +938,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -958,10 +976,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -981,10 +999,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1004,10 +1022,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1027,10 +1045,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1050,10 +1068,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1073,10 +1091,10 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1096,10 +1114,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1119,10 +1137,10 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1131,6 +1149,52 @@
         <v>10</v>
       </c>
       <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920117</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920130</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="61">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,27 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -100,13 +121,22 @@
     <t>ROJAS</t>
   </si>
   <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
   </si>
   <si>
     <t>TREJO</t>
@@ -124,16 +154,28 @@
     <t>BRAVO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
+    <t>CRISTIAN JAVIER</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>EDWIN YAMIL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
   </si>
   <si>
     <t>KEVIN ISAAC</t>
@@ -158,12 +200,6 @@
   </si>
   <si>
     <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
   </si>
 </sst>
 </file>
@@ -938,7 +974,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -970,16 +1006,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920005</v>
+        <v>20330051920005</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -993,22 +1029,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920393</v>
+        <v>21330051920078</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1016,16 +1052,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920071</v>
+        <v>21330051920103</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1039,22 +1075,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920077</v>
+        <v>21330051920117</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1062,22 +1098,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920082</v>
+        <v>21330051920130</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1085,22 +1121,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920094</v>
+        <v>21330051920036</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1108,22 +1144,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920098</v>
+        <v>21330051920037</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1131,71 +1167,186 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920100</v>
+        <v>21330051920005</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920117</v>
+        <v>21330051920393</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920130</v>
+        <v>21330051920071</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920077</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920082</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920094</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920098</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920100</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -79,127 +79,100 @@
     <t>CORTEZ</t>
   </si>
   <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>SANJUAN</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>ENCARNACION</t>
   </si>
   <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>LAGUNES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
     <t>CRISTIAN JAVIER</t>
   </si>
   <si>
+    <t>ANGEL YAIR</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
     <t>MIROSLAVA</t>
   </si>
   <si>
-    <t>ALMA KAREN</t>
-  </si>
-  <si>
     <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>EDWIN YAMIL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>VANESSA AMAIRANY</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>ALDO GEOVANNI</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
   </si>
 </sst>
 </file>
@@ -597,22 +570,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
         <v>28</v>
       </c>
       <c r="G2">
-        <v>82.34999999999999</v>
+        <v>80</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -626,19 +599,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>71.05</v>
+        <v>78.95</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -652,10 +625,10 @@
         <v>26</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>9</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>17</v>
@@ -664,7 +637,7 @@
         <v>65.38</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -678,19 +651,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>78.13</v>
+        <v>84.38</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -740,19 +713,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>74.29000000000001</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -766,16 +742,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>81.58</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -789,16 +768,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>69.23</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -812,16 +794,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
         <v>25</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>78.13</v>
+      </c>
+      <c r="H5">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -871,22 +856,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>82.34999999999999</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -900,19 +885,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>71.05</v>
+        <v>81.58</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -926,19 +911,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>65.38</v>
+        <v>69.23</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -952,10 +937,10 @@
         <v>32</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>7</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>25</v>
@@ -964,7 +949,7 @@
         <v>78.13</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -974,7 +959,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1012,10 +997,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1029,22 +1014,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920078</v>
+        <v>21330051920393</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1052,16 +1037,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920103</v>
+        <v>21330051920077</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1075,22 +1060,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920117</v>
+        <v>21330051920086</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1098,16 +1083,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920130</v>
+        <v>21330051920113</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1121,22 +1106,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920036</v>
+        <v>21330051920133</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1144,16 +1129,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920037</v>
+        <v>21330051920036</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1167,39 +1152,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920005</v>
+        <v>21330051920037</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920393</v>
+        <v>21330051920005</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1213,16 +1198,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920071</v>
+        <v>21330051920078</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1236,16 +1221,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920077</v>
+        <v>21330051920080</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1259,93 +1244,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920082</v>
+        <v>21330051920117</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920094</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920098</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920100</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="49">
   <si>
     <t>Mat</t>
   </si>
@@ -91,7 +91,7 @@
     <t>CERVANTES</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>ENCARNACION</t>
   </si>
   <si>
     <t>COMIHUA</t>
@@ -109,9 +109,6 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -124,7 +121,7 @@
     <t>RIVERA</t>
   </si>
   <si>
-    <t>MONTIEL</t>
+    <t>MONTALVO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
@@ -139,9 +136,6 @@
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
     <t>CRISTIAN JAVIER</t>
   </si>
   <si>
@@ -157,7 +151,7 @@
     <t>SAMANTHA MIA</t>
   </si>
   <si>
-    <t>CESAR DANIEL</t>
+    <t>DIANA IRAIS</t>
   </si>
   <si>
     <t>ALEJANDRO GABRIEL</t>
@@ -170,9 +164,6 @@
   </si>
   <si>
     <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
   </si>
 </sst>
 </file>
@@ -959,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -997,10 +988,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1020,10 +1011,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1043,10 +1034,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1066,10 +1057,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1092,7 +1083,7 @@
         <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1106,16 +1097,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920133</v>
+        <v>21330051920117</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1135,10 +1126,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1158,10 +1149,10 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1184,7 +1175,7 @@
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1204,10 +1195,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1227,10 +1218,10 @@
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1239,29 +1230,6 @@
         <v>10</v>
       </c>
       <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920117</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -94,6 +94,9 @@
     <t>ENCARNACION</t>
   </si>
   <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
     <t>COMIHUA</t>
   </si>
   <si>
@@ -124,6 +127,9 @@
     <t>MONTALVO</t>
   </si>
   <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -152,6 +158,9 @@
   </si>
   <si>
     <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>XOCHITL JOSELINE</t>
   </si>
   <si>
     <t>ALEJANDRO GABRIEL</t>
@@ -950,7 +959,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -988,10 +997,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1011,10 +1020,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1034,10 +1043,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1057,10 +1066,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1080,10 +1089,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1103,10 +1112,10 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1120,16 +1129,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920036</v>
+        <v>20330051920117</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1143,16 +1152,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920037</v>
+        <v>21330051920036</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1166,45 +1175,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920005</v>
+        <v>21330051920037</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920078</v>
+        <v>21330051920005</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1212,16 +1221,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920080</v>
+        <v>21330051920078</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1230,6 +1239,29 @@
         <v>10</v>
       </c>
       <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920080</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="49">
   <si>
     <t>Mat</t>
   </si>
@@ -76,9 +76,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CORTEZ</t>
-  </si>
-  <si>
     <t>URBINA</t>
   </si>
   <si>
@@ -112,9 +109,6 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>TREJO</t>
   </si>
   <si>
@@ -140,9 +134,6 @@
   </si>
   <si>
     <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAVIER</t>
   </si>
   <si>
     <t>ANGEL YAIR</t>
@@ -959,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -991,16 +982,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920005</v>
+        <v>21330051920393</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1014,22 +1005,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920393</v>
+        <v>21330051920077</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1037,16 +1028,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920077</v>
+        <v>21330051920086</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1060,22 +1051,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920086</v>
+        <v>21330051920113</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1083,16 +1074,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920113</v>
+        <v>21330051920117</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1106,22 +1097,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920117</v>
+        <v>20330051920117</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1129,16 +1120,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920117</v>
+        <v>21330051920036</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1152,16 +1143,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920036</v>
+        <v>21330051920037</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1175,45 +1166,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920037</v>
+        <v>21330051920005</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920005</v>
+        <v>21330051920078</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1221,16 +1212,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920078</v>
+        <v>21330051920080</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1239,29 +1230,6 @@
         <v>10</v>
       </c>
       <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920080</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -76,15 +76,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>URBINA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>CERVANTES</t>
   </si>
   <si>
@@ -109,15 +103,9 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>TREJO</t>
-  </si>
-  <si>
     <t>LAGUNES</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>MONTALVO</t>
   </si>
   <si>
@@ -136,13 +124,7 @@
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>ANGEL YAIR</t>
-  </si>
-  <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
   </si>
   <si>
     <t>SAMANTHA MIA</t>
@@ -567,16 +549,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>82.86</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -719,7 +701,7 @@
         <v>74.29000000000001</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -950,7 +932,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -982,22 +964,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920393</v>
+        <v>21330051920077</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1005,22 +987,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920077</v>
+        <v>21330051920113</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1028,22 +1010,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920086</v>
+        <v>21330051920117</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1051,22 +1033,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920113</v>
+        <v>20330051920117</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1074,22 +1056,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920117</v>
+        <v>21330051920036</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1097,16 +1079,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920117</v>
+        <v>21330051920037</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1120,116 +1102,70 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920036</v>
+        <v>21330051920005</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920037</v>
+        <v>21330051920078</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920005</v>
+        <v>21330051920080</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920078</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920080</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -79,36 +79,39 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>CERVANTES</t>
   </si>
   <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>LAGUNES</t>
   </si>
   <si>
     <t>MONTALVO</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>TEPOLE</t>
   </si>
   <si>
@@ -127,25 +130,28 @@
     <t>MARIA FERNANDA</t>
   </si>
   <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>NATALIE</t>
+  </si>
+  <si>
+    <t>XOCHITL JOSELINE</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
     <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>XOCHITL JOSELINE</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
   </si>
 </sst>
 </file>
@@ -932,7 +938,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -973,7 +979,7 @@
         <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -987,16 +993,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920113</v>
+        <v>21330051920117</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1010,16 +1016,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920117</v>
+        <v>21330051920120</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1039,10 +1045,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1062,10 +1068,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1085,10 +1091,10 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1108,10 +1114,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1128,13 +1134,13 @@
         <v>21330051920078</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1151,13 +1157,13 @@
         <v>21330051920080</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1166,6 +1172,29 @@
         <v>10</v>
       </c>
       <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920113</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
@@ -85,24 +85,24 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
     <t>CHAVEZ</t>
   </si>
   <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
     <t>LAGUNES</t>
   </si>
   <si>
@@ -112,21 +112,21 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>TEPOLE</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
@@ -136,22 +136,22 @@
     <t>NATALIE</t>
   </si>
   <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>SAMANTHA MIA</t>
+  </si>
+  <si>
     <t>XOCHITL JOSELINE</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920117</v>
+        <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920036</v>
+        <v>21330051920037</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -1085,13 +1085,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920037</v>
+        <v>21330051920005</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>41</v>
@@ -1100,21 +1100,21 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920005</v>
+        <v>21330051920078</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
         <v>42</v>
@@ -1123,7 +1123,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1131,16 +1131,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920078</v>
+        <v>21330051920080</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
         <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1154,22 +1154,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920080</v>
+        <v>21330051920113</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1177,13 +1177,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920113</v>
+        <v>20330051920117</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
         <v>44</v>
@@ -1192,7 +1192,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>1</v>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="48">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>COMIHUA</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>CAPORAL</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -134,6 +140,9 @@
   </si>
   <si>
     <t>NATALIE</t>
+  </si>
+  <si>
+    <t>LOGAN FRANCISCO</t>
   </si>
   <si>
     <t>ALEJANDRO GABRIEL</t>
@@ -938,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -976,10 +985,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -999,10 +1008,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1022,10 +1031,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1039,22 +1048,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920036</v>
+        <v>21330051920391</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1062,16 +1071,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920037</v>
+        <v>21330051920036</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1085,45 +1094,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920005</v>
+        <v>21330051920037</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920078</v>
+        <v>21330051920005</v>
       </c>
       <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1131,16 +1140,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920080</v>
+        <v>21330051920078</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1154,22 +1163,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920113</v>
+        <v>21330051920080</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1177,24 +1186,47 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920117</v>
+        <v>21330051920113</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920117</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
         <v>12</v>
       </c>
-      <c r="G11">
+      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -76,91 +76,73 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>COMIHUA</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>LAGUNES</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>VERA</t>
   </si>
   <si>
     <t>CAPORAL</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>DEL ROSARIO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>NATALIE</t>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>LOGAN FRANCISCO</t>
   </si>
   <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
     <t>ALEJANDRO GABRIEL</t>
   </si>
   <si>
     <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>SAMANTHA MIA</t>
-  </si>
-  <si>
-    <t>XOCHITL JOSELINE</t>
   </si>
 </sst>
 </file>
@@ -850,16 +832,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>74.29000000000001</v>
+        <v>80</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -876,16 +858,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>81.58</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -902,16 +884,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>69.23</v>
+        <v>80.77</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -928,16 +910,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -947,7 +929,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -979,16 +961,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920077</v>
+        <v>21330051920086</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1002,22 +984,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920117</v>
+        <v>21330051920094</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1025,22 +1007,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920120</v>
+        <v>21330051920109</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1054,10 +1036,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1071,68 +1053,68 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920036</v>
+        <v>21330051920005</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920037</v>
+        <v>21330051920078</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920005</v>
+        <v>21330051920036</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1140,93 +1122,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920078</v>
+        <v>21330051920037</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920080</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920113</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920117</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
   <si>
     <t>Mat</t>
   </si>
@@ -85,15 +85,21 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>COMIHUA</t>
   </si>
   <si>
@@ -109,12 +115,15 @@
     <t>VERA</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>CAPORAL</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -130,13 +139,19 @@
     <t>MARIA JOSE</t>
   </si>
   <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
     <t>LOGAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
   </si>
   <si>
     <t>ALEJANDRO GABRIEL</t>
@@ -929,7 +944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -967,10 +982,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -990,10 +1005,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1013,10 +1028,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1030,16 +1045,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920391</v>
+        <v>21330051920112</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1053,45 +1068,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920005</v>
+        <v>21330051920127</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920078</v>
+        <v>21330051920005</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1099,22 +1114,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920036</v>
+        <v>21330051920078</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1122,24 +1137,70 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920037</v>
+        <v>21330051920391</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920036</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
         <v>12</v>
       </c>
-      <c r="G9">
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920037</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -79,24 +79,21 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -109,18 +106,18 @@
     <t>RIVERA</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>BRAVO</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>CAPORAL</t>
   </si>
   <si>
@@ -133,22 +130,19 @@
     <t>FATIMA</t>
   </si>
   <si>
-    <t>INGRID AMERICA</t>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
   </si>
   <si>
     <t>LOGAN FRANCISCO</t>
@@ -944,7 +938,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -982,10 +976,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -999,22 +993,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920094</v>
+        <v>21330051920112</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1022,22 +1016,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920109</v>
+        <v>21330051920127</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1045,68 +1039,68 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920112</v>
+        <v>21330051920005</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920127</v>
+        <v>21330051920078</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920005</v>
+        <v>21330051920109</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1114,7 +1108,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920078</v>
+        <v>21330051920391</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
@@ -1123,13 +1117,13 @@
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1137,7 +1131,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920391</v>
+        <v>21330051920036</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -1146,13 +1140,13 @@
         <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1160,7 +1154,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920036</v>
+        <v>21330051920037</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
@@ -1169,7 +1163,7 @@
         <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1178,29 +1172,6 @@
         <v>12</v>
       </c>
       <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920037</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
         <v>1</v>
       </c>
     </row>
